--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:37</t>
+    <t xml:space="preserve">2026-09-09 22:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:23</t>
+    <t xml:space="preserve">2026-09-12 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:39</t>
+    <t xml:space="preserve">2026-09-24 00:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:17</t>
+    <t xml:space="preserve">2026-09-27 22:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:06</t>
+    <t xml:space="preserve">2026-09-29 11:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -577,7 +577,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>19.85</v>
+        <v>198.47</v>
       </c>
     </row>
     <row r="3">
@@ -594,7 +594,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>19.41</v>
+        <v>194.07</v>
       </c>
     </row>
     <row r="4">
@@ -611,7 +611,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>17.66</v>
+        <v>176.57</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17.49</v>
+        <v>174.92</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15.8</v>
+        <v>157.98</v>
       </c>
     </row>
     <row r="7">
@@ -662,7 +662,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>15.8</v>
+        <v>157.95</v>
       </c>
     </row>
     <row r="8">
@@ -679,7 +679,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>15.79</v>
+        <v>157.93</v>
       </c>
     </row>
     <row r="9">
@@ -696,7 +696,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>15.71</v>
+        <v>157.12</v>
       </c>
     </row>
     <row r="10">
@@ -713,7 +713,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>15.69</v>
+        <v>156.95</v>
       </c>
     </row>
     <row r="11">
@@ -730,7 +730,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>15.64</v>
+        <v>156.36</v>
       </c>
     </row>
     <row r="12">
@@ -747,7 +747,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>15.43</v>
+        <v>154.28</v>
       </c>
     </row>
     <row r="13">
@@ -764,7 +764,7 @@
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>15.3</v>
+        <v>153.02</v>
       </c>
     </row>
     <row r="14">
@@ -781,7 +781,7 @@
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15.15</v>
+        <v>151.45</v>
       </c>
     </row>
     <row r="15">
@@ -798,7 +798,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>15.02</v>
+        <v>150.16</v>
       </c>
     </row>
     <row r="16">
@@ -815,7 +815,7 @@
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>14.92</v>
+        <v>149.2</v>
       </c>
     </row>
     <row r="17">
@@ -832,7 +832,7 @@
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>14.89</v>
+        <v>148.87</v>
       </c>
     </row>
     <row r="18">
@@ -849,7 +849,7 @@
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>14.37</v>
+        <v>143.73</v>
       </c>
     </row>
     <row r="19">
@@ -866,7 +866,7 @@
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>14.03</v>
+        <v>140.27</v>
       </c>
     </row>
     <row r="20">
@@ -883,7 +883,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>13.9</v>
+        <v>139.01</v>
       </c>
     </row>
     <row r="21">
@@ -900,7 +900,7 @@
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>13.77</v>
+        <v>137.66</v>
       </c>
     </row>
     <row r="22">
@@ -917,7 +917,7 @@
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>13.66</v>
+        <v>136.61</v>
       </c>
     </row>
     <row r="23">
@@ -934,7 +934,7 @@
         <v>2021</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>13.62</v>
+        <v>136.24</v>
       </c>
     </row>
     <row r="24">
@@ -951,7 +951,7 @@
         <v>2021</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>13.34</v>
+        <v>133.4</v>
       </c>
     </row>
     <row r="25">
@@ -968,7 +968,7 @@
         <v>2021</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>13.13</v>
+        <v>131.32</v>
       </c>
     </row>
     <row r="26">
@@ -985,7 +985,7 @@
         <v>2021</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>13.1</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27">
@@ -1002,7 +1002,7 @@
         <v>2021</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>13.01</v>
+        <v>130.09</v>
       </c>
     </row>
     <row r="28">
@@ -1019,7 +1019,7 @@
         <v>2021</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>12.83</v>
+        <v>128.32</v>
       </c>
     </row>
     <row r="29">
@@ -1036,7 +1036,7 @@
         <v>2021</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>12.81</v>
+        <v>128.08</v>
       </c>
     </row>
     <row r="30">
@@ -1053,7 +1053,7 @@
         <v>2021</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>12.26</v>
+        <v>122.64</v>
       </c>
     </row>
     <row r="31">
@@ -1070,7 +1070,7 @@
         <v>2021</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>11.36</v>
+        <v>113.56</v>
       </c>
     </row>
     <row r="32">
@@ -1087,7 +1087,7 @@
         <v>2021</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>11.27</v>
+        <v>112.66</v>
       </c>
     </row>
     <row r="33">
@@ -1104,7 +1104,7 @@
         <v>2021</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>10.77</v>
+        <v>107.73</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:00</t>
+    <t xml:space="preserve">2026-10-01 19:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -159,7 +159,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:25</t>
+    <t xml:space="preserve">2026-10-02 13:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:07</t>
+    <t xml:space="preserve">2026-10-05 07:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
